--- a/daily_matches/job_matches_2026-08-23.xlsx
+++ b/daily_matches/job_matches_2026-08-23.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>DevSecOps Engineer</t>
+          <t>Java Full Stack Developer-Software Engineer II</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Claritas Rx</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>17.8</v>
+        <v>11.1</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>RAG, S3, EC2, Glue, Kinesis, CI/CD, GitHub Actions, Terraform, Git, PySpark</t>
+          <t>RAG, CI/CD, Git, Kafka, MongoDB, SQL, R, Java, Scala, Optimization</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,67 +496,67 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e12b8c592b8fca76</t>
+          <t>https://www.indeed.com/viewjob?jk=51af3dc634317edc</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Full Stack Cloud Engineer</t>
+          <t>Software Development Engineer 4</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Citi</t>
+          <t>Adobe</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>13.3</v>
+        <v>10</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>RAG, S3, Docker, Kubernetes, CI/CD, Jenkins, Git, NoSQL, SQL, R</t>
+          <t>Generative AI, RAG, Docker, CI/CD, Git, Python, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b84e015e4bbf3308</t>
+          <t>https://www.indeed.com/viewjob?jk=f7709ce54cf7d3e6</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Applied AI Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Soulside AI</t>
+          <t>Smart Apply Test Company</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, LLaMA, Mistral, Hugging Face, Prompt Engineering, PyTorch, Python, R, Optimization</t>
+          <t>AI Engineer, RAG, CI/CD, Git, PostgreSQL, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,147 +566,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15b10be8fa85df5f</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Solutions Architect - MENA</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Deepgram</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D5" t="n">
-        <v>10</v>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>RAG, Docker, Kubernetes, AKS, Git, Python, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>2026-08-22</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=d254d3c3f23fd186</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Government and Public Sector - Service Delivery Center - AI Solution Developer</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>EY</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>San Antonio, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D6" t="n">
-        <v>10</v>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>Generative AI, RAG, FastAPI, AKS, CI/CD, Python, SQL, R, Java</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a20acc5c777568e5</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Machine Learning Data Scientist</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Inabia Software &amp; Consulting Inc.</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D7" t="n">
-        <v>10</v>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>Data Scientist, Tableau, Power BI, Matplotlib, Python, SQL, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>2026-08-22</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ea90f0cb952f9858</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Senior Analyst, Search and Recommendations</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>CarMax</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Richmond, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D8" t="n">
-        <v>10</v>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>Data Scientist, Git, Databricks, Tableau, Matplotlib, Python, SQL, R, Hypothesis Testing</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>2026-08-22</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=cf8fa9b337456e62</t>
+          <t>https://www.indeed.com/viewjob?jk=f83179256865e3c1</t>
         </is>
       </c>
     </row>
